--- a/output/CLOTH01_summer/feeds_excel/simulation feeds/Inventory.xlsx
+++ b/output/CLOTH01_summer/feeds_excel/simulation feeds/Inventory.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>124</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SUP_002</t>
+          <t>SUP_001</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -578,17 +578,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>12.16</t>
+          <t>47.14</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>SUP_003</t>
+          <t>SUP_002</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -645,17 +645,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>15.91</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>28.37</t>
+          <t>39.77</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SUP_001</t>
+          <t>SUP_003</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -712,17 +712,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>14.87</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>37.17</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SUP_002</t>
+          <t>SUP_001</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -779,17 +779,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>32.74</t>
+          <t>24.49</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>81.85</t>
+          <t>64.44</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SUP_003</t>
+          <t>SUP_002</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>151</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SUP_002</t>
+          <t>SUP_001</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -913,17 +913,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>12.16</t>
+          <t>47.14</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SUP_003</t>
+          <t>SUP_002</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>15.91</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>28.37</t>
+          <t>39.77</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SUP_001</t>
+          <t>SUP_003</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>33</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1047,17 +1047,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>14.87</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>37.17</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SUP_002</t>
+          <t>SUP_001</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>32.74</t>
+          <t>24.49</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>81.85</t>
+          <t>64.44</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SUP_003</t>
+          <t>SUP_002</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>2367</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>SUP_002</t>
+          <t>SUP_001</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>127</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1244,17 +1244,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>12.16</t>
+          <t>47.14</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SUP_003</t>
+          <t>SUP_002</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>104</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1307,17 +1307,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>15.91</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>28.37</t>
+          <t>39.77</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SUP_001</t>
+          <t>SUP_003</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1370,17 +1370,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>14.87</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>37.17</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>SUP_002</t>
+          <t>SUP_001</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1433,17 +1433,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>32.74</t>
+          <t>24.49</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>81.85</t>
+          <t>64.44</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>SUP_003</t>
+          <t>SUP_002</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
